--- a/outputs/39046.xlsx
+++ b/outputs/39046.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="14">
   <si>
     <t xml:space="preserve">DATE</t>
   </si>
@@ -49,9 +49,6 @@
     <t xml:space="preserve">EGTRI010102</t>
   </si>
   <si>
-    <t xml:space="preserve">Yes</t>
-  </si>
-  <si>
     <t xml:space="preserve">DONY23</t>
   </si>
   <si>
@@ -59,9 +56,6 @@
   </si>
   <si>
     <t xml:space="preserve">FANDU7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No</t>
   </si>
   <si>
     <t xml:space="preserve">EGTRI0101</t>
@@ -158,32 +152,36 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -439,220 +437,229 @@
   <dimension ref="A1:L18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="8.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="24.91"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="23.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="14.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="8.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="24.91"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="23.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="14.43"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="3" t="n">
         <v>44570</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="4" t="str">
+        <f aca="false">IF(COUNTIF(D$2:D$6,"*"&amp;B2&amp;"*")&gt;0,"Yes","No")</f>
+        <v>Yes</v>
+      </c>
+      <c r="F2" s="5" t="n">
+        <f aca="false">COUNTIF(D$2:D$6,"*"&amp;B2&amp;"*")</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="n">
+        <v>44571</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="4" t="n">
-        <f aca="false">IF(C2="CANCELLED",SUMPRODUCT(--ISNUMBER(SEARCH(B2,$D$2:$D$6))),0)</f>
+      <c r="C3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="4" t="str">
+        <f aca="false">IF(COUNTIF(D$2:D$6,"*"&amp;B3&amp;"*")&gt;0,"Yes","No")</f>
+        <v>Yes</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <f aca="false">COUNTIF(D$2:D$6,"*"&amp;B3&amp;"*")</f>
         <v>2</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="n">
-        <v>44571</v>
-      </c>
-      <c r="B3" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="0" t="s">
+    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="n">
+        <v>44572</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="3" t="s">
+      <c r="E4" s="4" t="str">
+        <f aca="false">IF(COUNTIF(D$2:D$6,"*"&amp;B4&amp;"*")&gt;0,"Yes","No")</f>
+        <v>No</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <f aca="false">COUNTIF(D$2:D$6,"*"&amp;B4&amp;"*")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="n">
+        <v>44573</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="4" t="str">
+        <f aca="false">IF(COUNTIF(D$2:D$6,"*"&amp;B5&amp;"*")&gt;0,"Yes","No")</f>
+        <v>Yes</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <f aca="false">COUNTIF(D$2:D$6,"*"&amp;B5&amp;"*")</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="n">
+        <v>44574</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="4" t="n">
-        <f aca="false">IF(C3="CANCELLED",SUMPRODUCT(--ISNUMBER(SEARCH(B3,$D$2:$D$6))),0)</f>
+      <c r="C6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="4" t="str">
+        <f aca="false">IF(COUNTIF(D$2:D$6,"*"&amp;B6&amp;"*")&gt;0,"Yes","No")</f>
+        <v>Yes</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <f aca="false">COUNTIF(D$2:D$6,"*"&amp;B6&amp;"*")</f>
         <v>2</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="n">
-        <v>44572</v>
-      </c>
-      <c r="B4" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" s="4" t="n">
-        <f aca="false">IF(C4="CANCELLED",SUMPRODUCT(--ISNUMBER(SEARCH(B4,$D$2:$D$6))),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="n">
-        <v>44573</v>
-      </c>
-      <c r="B5" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" s="3"/>
-      <c r="F5" s="4" t="n">
-        <f aca="false">IF(C5="CANCELLED",SUMPRODUCT(--ISNUMBER(SEARCH(B5,$D$2:$D$6))),0)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="n">
-        <v>44574</v>
-      </c>
-      <c r="B6" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="E6" s="3"/>
-      <c r="F6" s="4" t="n">
-        <f aca="false">IF(C6="CANCELLED",SUMPRODUCT(--ISNUMBER(SEARCH(B6,$D$2:$D$6))),0)</f>
-        <v>2</v>
-      </c>
-    </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2"/>
+      <c r="A7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2"/>
+      <c r="A8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2"/>
+      <c r="A9" s="3"/>
     </row>
     <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2"/>
+      <c r="A10" s="3"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
-      <c r="I12" s="5"/>
-      <c r="J12" s="5"/>
-      <c r="K12" s="6"/>
-      <c r="L12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="6"/>
+      <c r="I12" s="6"/>
+      <c r="J12" s="6"/>
+      <c r="K12" s="7"/>
+      <c r="L12" s="7"/>
     </row>
     <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
-      <c r="I13" s="5"/>
-      <c r="J13" s="5"/>
-      <c r="K13" s="6"/>
-      <c r="L13" s="6"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6"/>
+      <c r="I13" s="6"/>
+      <c r="J13" s="6"/>
+      <c r="K13" s="7"/>
+      <c r="L13" s="7"/>
     </row>
     <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
-      <c r="I14" s="5"/>
-      <c r="J14" s="5"/>
-      <c r="K14" s="6"/>
-      <c r="L14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6"/>
+      <c r="I14" s="6"/>
+      <c r="J14" s="6"/>
+      <c r="K14" s="7"/>
+      <c r="L14" s="7"/>
     </row>
     <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
-      <c r="I15" s="5"/>
-      <c r="J15" s="5"/>
-      <c r="K15" s="6"/>
-      <c r="L15" s="6"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6"/>
+      <c r="H15" s="6"/>
+      <c r="I15" s="6"/>
+      <c r="J15" s="6"/>
+      <c r="K15" s="7"/>
+      <c r="L15" s="7"/>
     </row>
     <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
-      <c r="H16" s="5"/>
-      <c r="I16" s="5"/>
-      <c r="J16" s="5"/>
-      <c r="K16" s="6"/>
-      <c r="L16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6"/>
+      <c r="I16" s="6"/>
+      <c r="J16" s="6"/>
+      <c r="K16" s="7"/>
+      <c r="L16" s="7"/>
     </row>
     <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
-      <c r="H17" s="5"/>
-      <c r="I17" s="5"/>
-      <c r="J17" s="5"/>
-      <c r="K17" s="6"/>
-      <c r="L17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="6"/>
+      <c r="I17" s="6"/>
+      <c r="J17" s="6"/>
+      <c r="K17" s="7"/>
+      <c r="L17" s="7"/>
     </row>
     <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D18" s="6"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="6"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="6"/>
-      <c r="I18" s="6"/>
-      <c r="J18" s="6"/>
-      <c r="K18" s="6"/>
-      <c r="L18" s="6"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7"/>
+      <c r="H18" s="7"/>
+      <c r="I18" s="7"/>
+      <c r="J18" s="7"/>
+      <c r="K18" s="7"/>
+      <c r="L18" s="7"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
